--- a/experiment_results/wu_calibration/rtt_bursts_rps5_att4_WU100000.xlsx
+++ b/experiment_results/wu_calibration/rtt_bursts_rps5_att4_WU100000.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:010.1</t>
+          <t>00:009.8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>145</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:020.9</t>
+          <t>00:020.7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -590,27 +590,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:029.7</t>
+          <t>00:030.2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,17 +620,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:039.8</t>
+          <t>00:040.0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -704,27 +704,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:050.2</t>
+          <t>00:049.6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>21.7</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01:000.2</t>
+          <t>01:000.0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -771,17 +771,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -818,27 +818,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:010.1</t>
+          <t>01:010.0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,22 +848,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -875,27 +875,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:020.4</t>
+          <t>01:019.7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>142</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -932,27 +932,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:030.0</t>
+          <t>01:030.4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>129</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -989,27 +989,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:039.9</t>
+          <t>01:040.0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1046,27 +1046,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:049.9</t>
+          <t>01:050.3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,17 +1076,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01:059.8</t>
+          <t>01:059.9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1160,27 +1160,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:009.7</t>
+          <t>02:010.1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1217,22 +1217,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:020.0</t>
+          <t>02:019.9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:030.0</t>
+          <t>02:029.7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,22 +1304,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1331,7 +1331,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:038.7</t>
+          <t>02:039.3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1341,17 +1341,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1388,27 +1388,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:050.3</t>
+          <t>02:050.1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,17 +1418,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:055.2</t>
+          <t>02:055.4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1494,6 +1494,63 @@
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>Normal/Residual</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>03:000.3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>13.8</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>15.8</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>Normal/Residual</t>
         </is>
